--- a/template/template_fix.xlsx
+++ b/template/template_fix.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\server1\共用區\Mika\出貨單&amp;維修單\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Demo\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652C05D6-14F2-460F-B430-36715756556C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37820154-0AF8-4EC2-A80E-B8F03C3F365F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="3060" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="空白" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$1:$J$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$3:$J$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">空白!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="25">
   <si>
     <t>立善科技有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,30 +116,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Mika</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>出貨日期：　　　年　　月       日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">配件
-□充電器  □充電線
-□其他：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="細明體-ExtB"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>_____________</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -148,28 +125,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">2
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>富泰空調科技股份有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出貨日期：2026 年 3 月  17 日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新竹縣湖口鄉新竹工業區光復路58-1號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余文怡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 電動升降平台LT201020(面板改1200X3200mm)</t>
+    <t>出貨日期：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -181,7 +137,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -272,13 +228,6 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="細明體-ExtB"/>
-      <family val="1"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -591,6 +540,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -643,51 +637,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -714,7 +663,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="323850" cy="264560"/>
@@ -770,13 +719,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>790576</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -842,7 +791,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="838200" cy="266700"/>
@@ -904,7 +853,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>97155</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180975" cy="180975"/>
@@ -967,13 +916,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>154305</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -989,8 +938,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5240991" y="4444813"/>
-          <a:ext cx="509420" cy="471992"/>
+          <a:off x="4777068" y="4863913"/>
+          <a:ext cx="426496" cy="463027"/>
           <a:chOff x="5006340" y="4114800"/>
           <a:chExt cx="510540" cy="464820"/>
         </a:xfrm>
@@ -1099,13 +1048,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>300990</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>154305</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1160,13 +1109,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>605118</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>78442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>297628</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>143660</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1501,8 +1450,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5238750" y="4067175"/>
-          <a:ext cx="510540" cy="468630"/>
+          <a:off x="4773930" y="4069080"/>
+          <a:ext cx="430530" cy="464820"/>
           <a:chOff x="5006340" y="4114800"/>
           <a:chExt cx="510540" cy="464820"/>
         </a:xfrm>
@@ -1897,264 +1846,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:N15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" customWidth="1"/>
     <col min="6" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+    <row r="3" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+    </row>
+    <row r="4" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26" t="s">
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="31"/>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="J6" s="46"/>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27" t="s">
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="32"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="J7" s="47"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="29"/>
-      <c r="L6" s="13"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="44"/>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="5" t="s">
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="N8" s="14"/>
-    </row>
-    <row r="9" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="7"/>
+      <c r="L10" s="12"/>
+      <c r="N10" s="14"/>
+    </row>
+    <row r="11" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:14" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="26"/>
+      <c r="L11" s="13"/>
+    </row>
+    <row r="12" spans="1:14" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="42" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="42" t="s">
+      <c r="F12" s="24"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="42"/>
-      <c r="J10" s="47"/>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="I12" s="24"/>
+      <c r="J12" s="29"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="L11" s="12"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="L13" s="4"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="L15" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H12:J12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -2167,122 +2102,122 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B29E05-27D1-4E38-AE1C-126D1BD587A8}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" customWidth="1"/>
     <col min="6" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="10.75" customWidth="1"/>
-    <col min="9" max="9" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="31"/>
+      <c r="J4" s="46"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27" t="s">
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="32"/>
+      <c r="J5" s="47"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+    <row r="6" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="29"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="5" t="s">
         <v>2</v>
       </c>
@@ -2300,14 +2235,14 @@
       </c>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:12" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+    <row r="8" spans="1:12" ht="106.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="37"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="1"/>
@@ -2315,80 +2250,79 @@
       <c r="J8" s="7"/>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="26"/>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:12" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+    <row r="10" spans="1:12" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="42"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="42"/>
-      <c r="J10" s="47"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="29"/>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
       <c r="L11" s="12"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
       <c r="L13" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="F12:H13"/>
+    <mergeCell ref="I12:J13"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
@@ -2401,12 +2335,13 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="F12:H13"/>
-    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/template/template_fix.xlsx
+++ b/template/template_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Demo\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37820154-0AF8-4EC2-A80E-B8F03C3F365F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3995B062-C22A-4475-812C-A9518A9D48C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -494,7 +494,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -540,6 +540,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -585,58 +639,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1860,109 +1866,109 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="4" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
       <c r="L5" s="11"/>
     </row>
     <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41" t="s">
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="46"/>
+      <c r="J6" s="31"/>
       <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42" t="s">
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="47"/>
+      <c r="J7" s="32"/>
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="44"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="5" t="s">
         <v>2</v>
       </c>
@@ -1981,13 +1987,13 @@
       <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="19"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
         <v>23</v>
@@ -2002,69 +2008,79 @@
       <c r="A11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="26"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="44"/>
       <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:14" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="42"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="24"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="29"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="47"/>
       <c r="L12" s="12"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
       <c r="L13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
       <c r="L15" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H12:J12"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="A9:B9"/>
@@ -2080,16 +2096,6 @@
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="H12:J12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -2115,109 +2121,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
       <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41" t="s">
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="46"/>
+      <c r="J4" s="31"/>
       <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42" t="s">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="47"/>
+      <c r="J5" s="32"/>
       <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
       <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="5" t="s">
         <v>2</v>
       </c>
@@ -2236,13 +2242,13 @@
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" ht="106.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="1"/>
@@ -2254,75 +2260,76 @@
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="26"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="44"/>
       <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:12" ht="27.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="42"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="29"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="47"/>
       <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
       <c r="L11" s="12"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
       <c r="L13" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="F12:H13"/>
-    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
@@ -2335,13 +2342,12 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="F12:H13"/>
+    <mergeCell ref="I12:J13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
